--- a/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-triggeredbreaths.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="738">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-triggeredbreaths</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-triggeredbreaths</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -878,7 +878,7 @@
     <t>Code defined by a terminology system</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Rate of breaths or inspiratory gas flow initiated and terminated by the patient where pressure and flow/volume delivery are determined by the patient without support or assistance by the ventilator. Includes unassisted breaths that are superimposed on the intermittently elevated baseline pressure with APRV, bilevel or spontaneous-only modes.</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
@@ -1062,7 +1062,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1818,6 +1818,9 @@
     <t>Observation.bodySite.coding</t>
   </si>
   <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
     <t>Observation.bodySite.coding.id</t>
   </si>
   <si>
@@ -1909,7 +1912,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
@@ -13217,7 +13220,7 @@
         <v>274</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>580</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>276</v>
@@ -13313,10 +13316,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13437,10 +13440,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13563,10 +13566,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13668,7 +13671,7 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>84</v>
@@ -13691,10 +13694,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13794,7 +13797,7 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>84</v>
@@ -13817,10 +13820,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13920,7 +13923,7 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>84</v>
@@ -13943,10 +13946,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14069,10 +14072,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14197,10 +14200,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14325,10 +14328,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14354,16 +14357,16 @@
         <v>245</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14391,10 +14394,10 @@
         <v>162</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14412,7 +14415,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14439,10 +14442,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14453,10 +14456,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14479,16 +14482,16 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14538,7 +14541,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14562,27 +14565,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14605,16 +14608,16 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14664,7 +14667,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14688,27 +14691,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14731,19 +14734,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14792,7 +14795,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14804,7 +14807,7 @@
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14819,10 +14822,10 @@
         <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14833,10 +14836,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14957,10 +14960,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15083,14 +15086,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15112,10 +15115,10 @@
         <v>116</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>119</v>
@@ -15170,7 +15173,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15211,10 +15214,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15237,13 +15240,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15294,7 +15297,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15303,16 +15306,16 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>84</v>
@@ -15321,10 +15324,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15335,10 +15338,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15459,10 +15462,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15585,10 +15588,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15713,10 +15716,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15745,7 +15748,7 @@
         <v>457</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -15841,10 +15844,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15967,10 +15970,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16093,10 +16096,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16221,10 +16224,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16247,13 +16250,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16304,7 +16307,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16313,16 +16316,16 @@
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16331,10 +16334,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16345,10 +16348,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16469,10 +16472,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16595,10 +16598,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16723,10 +16726,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16755,7 +16758,7 @@
         <v>457</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
@@ -16851,10 +16854,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16977,10 +16980,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17103,10 +17106,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17231,10 +17234,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17260,16 +17263,16 @@
         <v>245</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17279,7 +17282,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17297,10 +17300,10 @@
         <v>176</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17318,7 +17321,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17342,10 +17345,10 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>557</v>
@@ -17359,10 +17362,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17388,16 +17391,16 @@
         <v>245</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17425,10 +17428,10 @@
         <v>162</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17446,7 +17449,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17470,10 +17473,10 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>557</v>
@@ -17487,10 +17490,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17513,17 +17516,17 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17572,7 +17575,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17602,7 +17605,7 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17613,10 +17616,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17642,10 +17645,10 @@
         <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17696,7 +17699,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17723,10 +17726,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17737,10 +17740,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17763,16 +17766,16 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17822,7 +17825,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17849,10 +17852,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -17863,10 +17866,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17889,16 +17892,16 @@
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17948,7 +17951,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -17975,10 +17978,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -17989,10 +17992,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18015,19 +18018,19 @@
         <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18076,7 +18079,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18103,10 +18106,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18117,10 +18120,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18241,10 +18244,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18367,14 +18370,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -18396,10 +18399,10 @@
         <v>116</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>119</v>
@@ -18454,7 +18457,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18495,10 +18498,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18524,13 +18527,13 @@
         <v>245</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>263</v>
@@ -18561,10 +18564,10 @@
         <v>162</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18582,7 +18585,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>95</v>
@@ -18606,7 +18609,7 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>267</v>
@@ -18623,10 +18626,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18649,16 +18652,16 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>427</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O127" t="s" s="2">
         <v>429</v>
@@ -18710,7 +18713,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18734,7 +18737,7 @@
         <v>84</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>432</v>
@@ -18751,10 +18754,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18780,13 +18783,13 @@
         <v>245</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O128" t="s" s="2">
         <v>542</v>
@@ -18838,7 +18841,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18847,7 +18850,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -18879,10 +18882,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18945,28 +18948,28 @@
         <v>153</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19007,10 +19010,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19036,16 +19039,16 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19094,7 +19097,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19121,10 +19124,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
